--- a/practice/answers/q020.xlsx
+++ b/practice/answers/q020.xlsx
@@ -70076,14 +70076,14 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>(c) The weighted average (62.6) is higher than the plain average (61.2).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>(d) The weighted average. It counts every acre once, so it is the yield of a typical wheat acre; the plain average counts every row once, so a variety grown on 200 acres in one municipality weighs as much as one grown on 20,000. The two differ because the widely grown rows yield a little better than the small ones, and the weighting lets those acres count for their true share.</t>

--- a/practice/answers/q020.xlsx
+++ b/practice/answers/q020.xlsx
@@ -70086,7 +70086,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>(d) The weighted average. It counts every acre once, so it is the yield of a typical wheat acre; the plain average counts every row once, so a variety grown on 200 acres in one municipality weighs as much as one grown on 20,000. The two differ because the widely grown rows yield a little better than the small ones, and the weighting lets those acres count for their true share.</t>
+          <t>(d) The weighted average. It counts every acre once, so it is the yield of a typical wheat acre; the plain average counts every row once, so a variety grown on 200 acres in one municipality weighs as much as one grown on 20,000. The two differ because, on balance, the heavily grown rows average slightly better yields, so letting acres count for their true share nudges the average up.</t>
         </is>
       </c>
     </row>
